--- a/data-manipulation-scripts/sheets-cleanup/sheets/RAIO 24_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/RAIO 24_02.xlsx
@@ -37,7 +37,7 @@
     <t>7895099122633</t>
   </si>
   <si>
-    <t>RZ IRON POP100 024513</t>
+    <t>RAIO DIANTEIRO IRON POP100 024513</t>
   </si>
   <si>
     <t>7895099126600</t>
@@ -158,7 +158,7 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
@@ -461,13 +461,15 @@
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C3" s="4">
         <v>1.0</v>
       </c>
-      <c r="D3" s="6"/>
+      <c r="D3" s="6">
+        <v>60.0</v>
+      </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -643,7 +645,9 @@
       <c r="C8" s="7">
         <v>1.0</v>
       </c>
-      <c r="D8" s="5"/>
+      <c r="D8" s="6">
+        <v>60.0</v>
+      </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
@@ -677,7 +681,9 @@
       <c r="C9" s="7">
         <v>1.0</v>
       </c>
-      <c r="D9" s="5"/>
+      <c r="D9" s="6">
+        <v>60.0</v>
+      </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
@@ -711,7 +717,9 @@
       <c r="C10" s="7">
         <v>1.0</v>
       </c>
-      <c r="D10" s="5"/>
+      <c r="D10" s="6">
+        <v>60.0</v>
+      </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
@@ -781,7 +789,9 @@
       <c r="C12" s="7">
         <v>1.0</v>
       </c>
-      <c r="D12" s="5"/>
+      <c r="D12" s="6">
+        <v>60.0</v>
+      </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
@@ -815,8 +825,8 @@
       <c r="C13" s="7">
         <v>1.0</v>
       </c>
-      <c r="D13" s="7">
-        <v>50.0</v>
+      <c r="D13" s="6">
+        <v>60.0</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
